--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="위험대장" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'위험대장'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'위험대장'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -109,12 +109,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEFC2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F1F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +199,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -638,7 +654,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>위험 14건 — 관찰 2 · 심각 6 · 주의 6</t>
+          <t>위험 16건 — 관찰 3 · 심각 6 · 주의 7</t>
         </is>
       </c>
     </row>
@@ -677,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1170,7 +1186,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>구현우선순위 P4-3</t>
+          <t>보완노트 §3.3</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1198,7 +1214,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>DXF 경로 우선(구현 완료). ODA 라이선스 확정 시 표본 변환 검증·손실 유형 목록화</t>
+          <t>플러그블 구조 완료(경로 env 만 설정하면 활성) — 라이선스 확보 전까지 501 정직 응답. 미구현 목록 잔여 1건이 이 항목(2026-07-25 기준 유일한 코드 잔여)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1458,7 +1474,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>PoC에서 BOM 전개·Run 파이프라인 실측 완료 — W35 성능시험으로 최종 검증</t>
+          <t>**종결(2026-07-25)** — 실측 BOM 전개 46.5req/s·p95 138ms(목표 30s 대비 여유), 핵심 쿼리 전량 인덱스 백업 EXPLAIN 확인. 상설 감시: tests/load_baseline.py. 고객 실데이터 규모 확보 시 재측정</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1466,9 +1482,9 @@
           <t>QA·인프라</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>감시</t>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>종결</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1483,7 +1499,7 @@
           <t>R-12</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>자원</t>
         </is>
@@ -1548,7 +1564,7 @@
           <t>R-13</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>외부</t>
         </is>
@@ -1610,22 +1626,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>R-14</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
+          <t>R-15</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>외부</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>이행 기간 중 원천 데이터 변경 — 이행본과 운영본 불일치</t>
+          <t>AI 기능 활성화가 외부 크레딧에 종속 — 충전·조직 설정 문제로 합성 기능 사용 불가 상태 지속 가능</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>데이터이행계획서 §6</t>
+          <t>C9 진단 이력(미구현목록)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1653,27 +1669,157 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
+          <t>**설계로 완화됨** — 크레딧 없어도 검색 근거·샘플 초안 제공하고 합성만 사유와 함께 보류(live_ai_degrade 6체크 상설 감시). 해제 시 코드 변경 없이 자동 전환. 트리거: 크레딧 차단 지속 시 조직·워크스페이스 한도 확인 후 지원 문의</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>PM·인프라</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>R-16</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>배포 중단이 로그 없이 발생 — systemd TimeoutStartSec 초과 시 빌드가 조용히 종료</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>9.53 실측(autodeploy)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — TimeoutStartSec 900→2400 상향 적용·설치배포매뉴얼 명문화. 부수 발견: 배포 확인 시 journalctl 시간 필터 누락하면 과거 실패를 오탐 → 매뉴얼에 --since 필수 기재</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>R-14</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>이행 기간 중 원천 데이터 변경 — 이행본과 운영본 불일치</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>데이터이행계획서 §6</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
           <t>기준일(cut-off) 합의 + 증분 이행 1회 계획 반영</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>DBA·고객사</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1818,6 +1818,207 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>설치 시 필수 시크릿 미설정 — 세션 토큰 서명 키가 소스 공개 기본값으로 동작하면 ADMIN 토큰 위조로 인증이 무력화된다</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>9.95 실측(운영 서버 기본 키 사용 확인)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — EDIM_SECRET 미설정 시 백엔드 기동 거부(개발만 EDIM_DEV_MODE=1). 운영 키 회전 완료. 트리거: 신규 고객 설치 시 .env.example·설치 매뉴얼 §환경변수 확인, 키 유출 의심 시 재발급·재기동으로 전 세션 무효화</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>고객사 DB 유출 시 비밀번호 전량 복원 — 솔트·스트레칭 없는 해시는 오프라인 대입에 무방비</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>9.96 코드 점검(로그인 경로)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — PBKDF2-HMAC-SHA256 260k+계정별 솔트로 교체, 구형식은 로그인 시 자동 승격(일괄 재설정 불요). 트리거: 하드웨어 성능 향상에 맞춰 반복수 주기 재검토(상향 시 다음 로그인에 자동 재계산)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>비밀번호 분실 시 복구 수단 부재 — 고객사 운영에서 반드시 발생하나 DB 직접 수정 외 방법이 없었다</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>9.97 기능 점검(재설정 경로 부재)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — 관리자 비밀번호 재설정 신설(임시 12자·잠금 동시 해제·감사 PW_RESET). 트리거: 유일 ADMIN 계정이 분실·잠금되는 단일 실패점 — 고객사에 ADMIN 2계정 이상 운영 권고</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>PM·운영</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2019,6 +2019,73 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>R-20</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>기존 테스트가 얕은 경로만 검증해 조용한 데이터 손상을 놓침 — 이동은 리프 1회만 검증되어 하위 주소 미갱신·순환 생성이 드러나지 않았다</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>10.3~10.5 실증(운영 서버)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — 쓰기가 여러 행에 번지는 연산은 ①하위/연쇄 대상이 실제로 따라왔는지 ②거부 경로가 부분 변경을 남기지 않는지까지 검증하도록 스위트 신설(이동 20·복제 17). 트리거: 트리·주소·계층에 손대는 신규 기능은 리프 1건이 아니라 2단 이상 하위를 가진 노드로 검증할 것</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>개발·QA</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2086,6 +2086,73 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>R-21</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>데이터 정합</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>구성(BOM·계층) 순환이 조용히 원가·소요량을 적게 만든다 — 재귀 전개가 순환 간선을 버리므로 화면에는 오류가 없다</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>10.9 실증(운영 서버 B→A 201 등록)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-25)** — 관계 등록 시 간접 순환까지 차단(승인 상태 불문), 전개 무결성(순환 간선·깊이 상한)을 실제 계산해 보고하고 미통과 시 승인 진행 차단. 트리거: 재귀 전개에 깊이 상한·seen 가드를 두는 곳은 **버린 사실을 반드시 응답에 고지**할 것(응답 정직성 규약)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2153,73 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>R-22</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>원가·견적</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>단가 미해결 품목이 0 원으로 집계돼 견적이 실제보다 싸 보인다 — 재료비→직접경비→매출로 축소가 전파되고 보고서에는 표시가 없다</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>11.6 실증(운영 데이터 1건 적발: KAD 900 FW-13-15)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 미해결 목록을 원가 상세에 영속하고 PCR 생성·목록·비교·분해 전 경로에 근거 완전성 전달, UI 경고 표시. 근거 완전성은 원가 마스킹 대상에서 제외. 트리거: 미해결이 보고되면 단가 대장에 해당 코드를 등재한 뒤 Run 재실행 — 표시가 사라지는지로 확인</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>영업·구매</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2220,6 +2220,140 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>R-23</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>원가·견적</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Run 이 견적안의 제품을 무시하고 고정 제품으로 원가를 계산 — 제품이 둘 이상인 고객사에서 모든 견적이 같은 원가가 된다</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>12.4 실증(FDV-480 견적안 로그)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 견적안 product_code_id 를 Run 루트·제조비 도면 조회에 사용, 폴백은 견적안에 제품이 없을 때로 한정. 트리거: 데모 데이터가 단일 제품이라 이런 하드코딩은 테스트로 안 드러난다 — 신규 파이프라인은 **제품 2종 이상**으로 검증할 것</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>R-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>운영·데이터</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>컨테이너 기본 시간대(UTC)와 업무 시간대(KST) 불일치로 날짜가 하루 밀림 — 00~09시에만 재현돼 평소 점검으로는 드러나지 않는다</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>12.1 실측(단가 valid_from 전일 저장)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — DB 세션·컨테이너 TZ 를 EDIM_TZ(기본 Asia/Seoul)로 통일, /system/status businessDate 진단 + 상시 스위트. 트리거: 신규 환경 구축 시 businessDate.aligned 를 배포 직후 확인, 해외 고객사는 EDIM_TZ 만 변경</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2354,6 +2354,140 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>R-25</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>보안·통제</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>통제를 새로 넣을 때 같은 데이터에 닿는 다른 경로를 빠뜨려 우회로가 남는다 — 렌더 PDF 는 막히는데 같은 금액의 산출물 파일은 그대로 다운로드됐다</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>15.1 실증(no_download 상태에서 /files/download 200·25KB)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 산출물 폴더→정보그룹 매핑으로 파일 다운로드에 동일 통제 적용, 회귀 고정(차단 403·ADMIN 200). 트리거: **통제를 추가·변경할 때 같은 데이터에 닿는 경로를 전부 세어 본다**(조회·렌더·파일·export·목록). 8.3(마스킹 19경로 중 3곳)·15.1(다운로드)이 같은 원인이었다</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>개발·보안</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>R-26</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>가용성</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>업로드 크기 상한 부재 — Excel Import 가 파일 전체를 메모리로 읽어 큰 파일 하나로 프로세스 메모리가 고갈될 수 있다</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>15.1 점검(업로드 10곳 중 6곳 무제한)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — _read_upload() 공용 헬퍼로 20MB 상한·빈 파일 422, 초과 시 413 에 크기와 상한 병기. 7곳 적용. 트리거: 신규 업로드 엔드포인트는 반드시 _read_upload() 를 거칠 것 — 직접 uploadedFile.read() 를 호출하면 상한이 없다</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2488,6 +2488,140 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>R-27</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>데이터 정합</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>낙관적 잠금을 한 경로에만 걸어 다른 쓰기 경로의 변경이 토큰에 반영되지 않는다 — 잠금이 걸려 있는데 조용히 덮어써진다</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>16.7 실증(치수 저장이 macro version 미증가)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 같은 데이터를 바꾸는 모든 경로에서 version 증가, 회귀는 "다른 경로의 변경이 잠금에 보이는가" 로 고정. 트리거: **잠금 토큰을 도입하면 그 컬럼을 바꾸는 쓰기 경로를 전수로 세어 본다** — 하나라도 토큰을 올리지 않으면 잠금은 장식이다</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>R-28</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>정직성</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>목록이 상한에서 조용히 잘려 전체를 세는 통계와 어긋난다 — 사용자는 두 화면의 수치 불일치를 데이터 오류로 오해한다</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>16.9 실측(Run 목록 1000 vs 통계 491+524)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 목록형은 X-Truncated 헤더, 객체형은 본문 truncated 로 고지. 트리거: **두 수치를 대조하는 화면이 있으면 그 목록은 완전성이 판단에 쓰인다** — 상한을 두려면 절단을 반드시 알릴 것</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,9 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2622,6 +2628,140 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>R-29</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>데이터 정합</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>상태·구분 컬럼의 허용 집합이 애플리케이션에만 있어 잘못된 값이 저장돼도 막히지 않는다 — 이후 조회가 그 행을 걸러 내므로 오류가 아니라 '실종'으로 나타난다(승인했는데 목록에 없다)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>17.1 실측(핵심 상태 컬럼 6개 중 4개에 CHECK 없음)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 0058 로 product_code·code_relationship·code_item_value·cst_quotation 에 CHECK 추가(규격+코드 쓰기 경로 합집합). 트리거: 상태·구분 성격의 컬럼을 새로 만들거나 허용 값을 늘릴 때 — 마이그레이션에 CHECK 를 함께 넣고, 코드의 쓰기 경로를 전수로 모아 집합을 정한다(빠뜨리면 정상 경로가 500 이 된다).</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>R-30</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>문서 신뢰성</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>코드에서 뽑는 문서의 추출원이 실제 데이터의 일부만 덮으면, 빠진 부분은 빈 칸이 아니라 행 자체가 사라져 읽는 사람이 누락을 알아챌 수 없다</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>17.2 실측(base_schema.sql 의 기준 테이블 34개가 거버넌스 정의서에서 누락)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 생성기가 base_schema.sql + alembic, CREATE TABLE + ALTER TABLE 을 모두 읽는다. 게이트에 '미분류가 있으면 실패' 추가(문서·코드가 똑같이 미분류면 드리프트 비교는 통과하므로 별도 조건이 필요). 트리거: 스키마·라우터의 원본 위치가 늘어날 때 — 생성기의 추출원 목록을 함께 늘리고, 재생성 후 행 수 변화를 확인한다.</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2762,6 +2762,73 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>R-31</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>보안(테넌트 격리)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>사용자가 보낸 대상 ID(target_id)를 확인 없이 저장한 뒤, 이후 처리에서 그 값을 신뢰해 다른 테넌트의 데이터를 변경한다 — '요청 행이 테넌트 범위이므로 대상도 안전하다' 는 추론이 성립하지 않는 지점</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>17.3 실증(테넌트1 관리자가 테넌트2 제품코드 상태 전이, 복구 완료)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 요청 생성 시 대상 소유 확인(미지원 대상 테이블은 422), 결정 반영 UPDATE 에 tenant_id 조건 추가. 트리거: 사용자가 보낸 ID 를 저장했다가 나중에 쓰는 구조를 만들 때 — 저장 시점에 소유를 확인하고, 사용 시점에도 테넌트 조건을 건다. 기준선에 등록된 테넌트 예외를 볼 때는 **그 예외의 근거가 되는 전제를 반대편 코드에서 직접 확인한다** (이 건도 예외 근거 자체가 틀렸다).</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2829,73 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>R-32</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>데이터 정합</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>미결 상태로 대기하는 요청(승인·반려 등)을 처리할 때 대상의 현재 상태를 확인하지 않아, 대기 중에 일어난 변경이 조용히 되돌아간다. 조건부 UPDATE 로 막아도 0행 사실이 어디에도 남지 않으면 '했다고 답하고 아무것도 안 한' 상태가 된다</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>17.6 정적 확인(6개 전이 분기 중 2개만 상태 조건 보유)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 승인은 반영 전 상태 확인 후 409, 반려는 요청만 닫고 자산은 조건부, 전이 여부를 sys_history.after_data.targetChanged 에 기록. 트리거: 결정·적용이 요청 시점과 분리되는 기능을 만들 때 — 적용 시점에 대상 상태를 확인하고, 적용하지 않았다면 그 사실을 응답이나 이력에 남긴다.</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -2780,7 +2780,7 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>17.3 실증(테넌트1 관리자가 테넌트2 제품코드 상태 전이, 복구 완료)</t>
+          <t>17.3 정적 확인(요청 생성에 소유 검증 없음 + _apply_decision 에 테넌트 조건 없음). 최초 보고한 '교차 테넌트 실증' 은 계정·대상이 모두 같은 테넌트였던 잘못된 시연으로 17.8 에서 정정 — 실행 실증은 없다</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J32" s="20" t="inlineStr">
         <is>
-          <t>**해소(2026-07-26)** — 요청 생성 시 대상 소유 확인(미지원 대상 테이블은 422), 결정 반영 UPDATE 에 tenant_id 조건 추가. 트리거: 사용자가 보낸 ID 를 저장했다가 나중에 쓰는 구조를 만들 때 — 저장 시점에 소유를 확인하고, 사용 시점에도 테넌트 조건을 건다. 기준선에 등록된 테넌트 예외를 볼 때는 **그 예외의 근거가 되는 전제를 반대편 코드에서 직접 확인한다** (이 건도 예외 근거 자체가 틀렸다).</t>
+          <t>**해소(2026-07-26, 근거는 정적 확인)** — 요청 생성 시 대상 소유 확인(미지원 대상 테이블은 422), 결정 반영 UPDATE 에 tenant_id 조건 추가. 트리거: 사용자가 보낸 ID 를 저장했다가 나중에 쓰는 구조를 만들 때 — 저장 시점에 소유를 확인하고, 사용 시점에도 테넌트 조건을 건다. 기준선에 등록된 테넌트 예외를 볼 때는 **그 예외의 근거가 되는 전제를 반대편 코드에서 직접 확인한다** (이 건도 예외 근거 자체가 틀렸다).</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2896,6 +2896,207 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>R-33</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>정직성</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>상한 판정 기준이 실제 적용 상한과 달라, 잘라 놓고 '완전하다'(X-Truncated: 0)고 적극적으로 답한다 — 침묵보다 오해를 부른다</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>17.10 실측(감사 XLSX 기본 1,000행 절단 · 판정 기준은 50,000)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — _xlsx_response 가 적용 상한(cap)을 받고 X-Limit 을 함께 돌려준다. 트리거: 호출부가 공통 상한보다 낮은 상한을 쓸 때 — 판정 기준도 함께 넘긴다. 같은 데이터의 다른 표현(JSON/XLSX/PDF)이 있으면 절단 고지가 양쪽에 있는지 대조한다.</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M34" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>R-34</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>보안(열람 통제)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>저장하지 않는 출력(미리보기·즉석 렌더)은 통제 대상에서 빠뜨리기 쉽다 — 담긴 데이터가 같으면 저장 여부와 무관하게 같은 통제를 받아야 한다</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>17.10 실측(견적 미리보기 PDF 에 단가·합계가 무통제로 실림)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — /cpq/quote-preview.pdf 에 price·quote 확인 추가. 트리거: 새 출력 경로(PDF·XLSX·ZIP·미리보기)를 만들 때 — 담기는 데이터의 정보그룹을 먼저 정하고, 통제 헬퍼 이름을 전수로 뽑아 기존 경로와 대조한다(헬퍼를 하나라도 빠뜨리면 분류가 틀린다).</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M35" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>R-35</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>같은 종류의 검사를 여러 곳에 인라인으로 두면 한쪽만 자라난다 — 나중에 추가된 검사가 기존 인라인 지점에는 반영되지 않는다</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>17.12 실측(빈 파일 검사가 Excel Import 에만 있어 0바이트 첨부가 등록됨)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 업로드 3경로를 _read_upload 하나로 합침(상한만 인자로 분리). 트리거: 검증·상한·정규화처럼 '어디서나 같아야 하는' 검사를 추가할 때 — 인라인으로 두지 말고 헬퍼로 만들고, 같은 검사를 하는 다른 지점을 먼저 찾아 합친다.</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M36" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3097,6 +3097,73 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>R-36</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>검증 신뢰성</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>검증 실행 중에 배포가 나가면 결과가 제품 상태를 반영하지 않는다 — 실패가 재시작 탓일 수 있고, 반대로 재시작 중 우연히 통과하면 실패했어야 할 실행이 초록으로 보인다. '중간 배포 없음' 을 사람의 기억에 맡기면 확인되지 않는다</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>18.4 실측(같은 게이트가 두 번 오탐 · 직전 90분간 배포 7회)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J37" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — /health.proc(기동 시 난수)을 러너가 시작·종료에 비교, 다르면 초록도 exit 1. 읽지 못하면 '확인하지 못했다' 명시. 트리거: 검증 결과를 근거로 쓸 때 — 그 실행이 깨끗했는지(재시작 경고 0건·exit 0)를 먼저 확인한다. 플릿 실행 중에는 푸시하지 않는다.</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3164,6 +3164,73 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>R-37</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>문서 신뢰성</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>설계 문서가 구현과 다른 식별자 체계를 쓰면서 '커버리지 100%' 를 주장한다 — 연결은 문서 안에서만 성립하고 코드로는 따라갈 수 없다. 문서를 보고 연동하면 404 를 만난다</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>18.6 실측(API 108중 42 일치 · 화면 ID 99/103 불일치 · 메뉴 기능코드 26/89)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-26)** — API 는 as-built 생성으로 전환(게이트 신설), 추적표 커버리지는 고리별 실측치로 교체해 과대 주장 제거. **잔여: 화면·기능코드 체계 통일은 결정 사항**(Launch 차단 #81). 트리거: 문서에 '전부·100%' 를 쓸 때 — 무엇과 무엇 사이의 연결인지 명시하고, 그 연결을 코드에서 실제로 따라가 본다. 못 이으면 못 이었다고 적는다.</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>개발/고객</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3231,6 +3231,73 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>R-38</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>데이터 정합(재현성)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>산출물 지문에 생성 시각 같은 휘발성 값이 섞이면 같은 입력이어도 지문이 달라진다 — '재실행해도 같은 값' 전제가 깨지고 납품물 동일성 대조가 거짓 변경으로 나온다. 게다가 시간 granularity 안에서는 일치하므로 검증이 운으로 통과한다</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>18.10 실측(DXF $TDCREATE·$TDUPDATE, 초 경계에서만 불일치)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-26)** — 헤더 휘발성 변수 9종을 지문에서 제외, 결정성 검증은 초 경계를 일부러 넘긴다. 트리거: 산출물 지문·비교를 만들 때 — 포맷이 시각·GUID·핸들 같은 값을 심는지 확인하고 제외한다. 결정성 검증은 **깨질 조건을 일부러 만들어** 확인한다(붙여서 두 번 호출하면 대개 통과한다).</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3298,6 +3298,73 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>R-39</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>감사 추적</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>삭제 감사에 대상 식별자만 남기면 원본이 사라진 뒤 '무엇이 지워졌는지' 를 어디에서도 복원할 수 없다 — 금액·납기 이의 제기에 답할 근거가 없어진다</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>18.16 전수 점검(삭제 34곳 중 30곳이 before 미보존)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 잔여는 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M40" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3346,7 +3346,7 @@
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 잔여는 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
+          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 18.19 로 신원·권한·금액·코드 4종 추가(사용자·역할·견적·제품코드). 잔여 19곳은 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
         </is>
       </c>
       <c r="K40" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3365,6 +3365,73 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>R-40</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>정직성(연쇄 연산)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>연쇄 삭제가 무엇을 함께 지웠는지 알리지 않으면, 사용자는 대상 하나만 지운 줄 알고 이후 자료가 비는 이유를 찾지 못한다. 감사에도 남지 않으면 사후 복원 판단도 불가</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>18.21 실측(도면 삭제가 자식 6곳을 건드리는데 응답은 도면번호뿐)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 단계별 rowcount 를 응답 cascade 와 감사 before 에 기록. 트리거: 한 요청이 다른 테이블 행까지 지우거나 연결을 끊을 때 — 무엇을 얼마나 건드렸는지 응답과 이력에 함께 남긴다. 정적 게이트가 볼 수 있도록 **테이블명을 변수로 조립하지 않는다** (f-string 으로 묶으면 그 문장이 검사에서 사라진다).</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M41" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3346,7 +3346,7 @@
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 18.19 로 신원·권한·금액·코드 4종 추가(사용자·역할·견적·제품코드). 잔여 19곳은 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
+          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 18.19 로 신원·권한·금액·코드 4종 추가(사용자·역할·견적·제품코드). 18.21 로 연쇄 범위 3종(도면·문서·프로젝트), 18.23 으로 수식·객체경로·Head 유형 3종 추가. 잔여 13곳은 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
         </is>
       </c>
       <c r="K40" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3346,7 +3346,7 @@
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 18.19 로 신원·권한·금액·코드 4종 추가(사용자·역할·견적·제품코드). 18.21 로 연쇄 범위 3종(도면·문서·프로젝트), 18.23 으로 수식·객체경로·Head 유형 3종 추가. 잔여 13곳은 위험 순으로 계속. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
+          <t>**부분 해소(2026-07-26)** — 계산 근거 기준값 5종(환율·세율·공휴일·부품 대체·BOM 관계)에 before 보존. 18.19 로 신원·권한·금액·코드 4종 추가(사용자·역할·견적·제품코드). 18.21 로 연쇄 범위 3종(도면·문서·프로젝트), 18.23 으로 수식·객체경로·Head 유형 3종 추가. 18.25 로 부품·창고·Templet·견적안 4종 추가. 잔여 9곳(계층 노드·Arrangement 구성품·공정 노드·slot-map·계약·패키지 항목·Head 바인딩/설계초기화·잠금 해제)은 성격상 위험이 낮아 후순위. 트리거: DELETE 엔드포인트를 만들 때 — RETURNING 으로 지운 값을 받아 before 에 넣는다(대부분 이미 RETURNING 을 쓰고 있으므로 추가 비용이 없다). 주석이 '무엇이 달라진다' 고 적었으면 그 값이 before 에 실제로 있는지 확인한다.</t>
         </is>
       </c>
       <c r="K40" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3432,6 +3432,73 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>R-41</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>감사 추적(수정)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>수정 감사가 새 값만 남기면 '왜 결과가 달라졌나' 를 되짚을 수 없다. 이전 값으로 거슬러 올라가는 방법도 같은 데이터를 바꾸는 다른 경로가 있으면 사슬이 끊긴다</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>18.29 전수 점검(수정 48곳 중 before 13곳)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 잔여 26곳은 위험 순으로 계속. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M42" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J42" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 잔여 26곳은 위험 순으로 계속. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
+          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 18.31 로 계정 활성 전환·공정 정의 2종 추가(누적 6종). 잔여 22곳 중 2곳은 from/to 를 이미 담아 대상 아님으로 확인 — **필드명이 아니라 정보가 완전한지로** 판단한다. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
         </is>
       </c>
       <c r="K42" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3499,6 +3499,140 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>R-42</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>기능 정합</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>검사·판정 기능의 규칙 데이터가 엔진 규약과 다른 형태면 '항상 통과' 가 된다 — 화면에는 검증이 도는 것처럼 보이고 경고 문구도 있으나 실제로는 아무것도 걸러지지 않는다</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>18.36 운영 실측(한계 1,500 대비 8,100 이 합격)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J43" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 판정 전용 매크로로 교체(0060), 임계값 회귀 검증 신설. 트리거: 규칙·정책을 데이터로 두는 기능을 만들 때 — 엔진 규약(무엇이 통과인가)을 문서화하고 **위반 사례로 실제 불합격이 나오는지** 확인한다. 통과만 확인하면 항상 통과하는 규칙도 통과로 보인다.</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M43" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>R-43</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>배포 신뢰성</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>마이그레이션이 실패해도 앱이 뜨면 /health 가 ok 를 돌려줘 배포가 성공으로 보인다 — 코드와 스키마가 어긋난 채 운영되고, 검증이 실패하면 제품이 아니라 검증을 의심하게 된다</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>18.37 실측(0060 롤백 · 배포 성공 표시)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J44" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — /health 에 schema 상태 노출, 플릿이 head 를 확인. 가용성(마이그레이션 실패 시에도 기동)은 유지. 트리거: 기동 시 하는 일이 실패해도 앱이 뜨는 구조를 만들 때 — 그 결과를 상태로 드러내고 배포·검증이 판단하게 한다.</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M44" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J42" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 18.31 로 계정 활성 전환·공정 정의 2종 추가(누적 6종). 잔여 22곳 중 2곳은 from/to 를 이미 담아 대상 아님으로 확인 — **필드명이 아니라 정보가 완전한지로** 판단한다. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
+          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 18.31 로 계정 활성 전환·공정 정의 2종 추가(누적 6종). 18.33·18.41 로 발주 승인·테넌트·Head·프로젝트·Contract 5종 추가(누적 11종). 잔여 15곳 중 2곳은 from/to 를 이미 담아 대상 아님으로 확인 — **필드명이 아니라 정보가 완전한지로** 판단한다. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
         </is>
       </c>
       <c r="K42" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J42" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-27)** — 매크로 수식·치수·정보접근 모드·제품코드 승인상태 4종에 before 추가. 18.31 로 계정 활성 전환·공정 정의 2종 추가(누적 6종). 18.33·18.41 로 발주 승인·테넌트·Head·프로젝트·Contract 5종 추가(누적 11종). 잔여 15곳 중 2곳은 from/to 를 이미 담아 대상 아님으로 확인 — **필드명이 아니라 정보가 완전한지로** 판단한다. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담는다. **같은 데이터를 바꾸는 다른 경로가 있으면 그쪽도 함께** 고친다(한쪽만 남기면 이력 사슬이 끊긴다).</t>
+          <t>**해소(2026-07-27)** — 위험 순으로 14종에 before 보존: 매크로 수식·치수·정보접근 모드·제품코드 승인상태·계정 활성·공정 MAKE/BUY·발주 승인 금액·테넌트 요금제·Head 권한 임계값·프로젝트 단계·Contract 선언·설계 파라미터·로트 유효기한·문서 채번 규칙. 잔여 12곳은 **대상 아님으로 판정**하고 근거를 남긴다: ① 비밀번호 변경은 값을 남기지 않는 것이 정답(해시라도 유출 시 대입 대상) ② 견적·문서 상태는 after 에 from/to 를 담아 이미 완전 ③ 개인 메뉴 설정·테넌트 UI(branding/headnav/leftnav)·번역 오버레이·이벤트 재배정·마일스톤 완료 표시는 업무 판단의 근거가 아니라 표시 상태다 ④ 계층/공정 노드는 구조 변경이나 이동·삭제 경로에 이미 이력이 있다. 트리거: 값을 바꾸는 엔드포인트를 만들 때 — 바꾸기 전 값을 먼저 읽어 before 에 담고, **같은 데이터를 바꾸는 다른 경로도 함께** 고친다(한쪽만 남기면 사슬이 끊긴다). 판정은 필드명이 아니라 **정보가 완전한지**로 한다.</t>
         </is>
       </c>
       <c r="K42" s="20" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>종결</t>
         </is>
       </c>
       <c r="M42" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3633,6 +3633,73 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>R-44</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>데이터 정합(재시도)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>생성 요청이 재시도·더블클릭으로 두 번 처리되면 금액·권한이 중복된다. 개발표준이 Idempotency-Key 를 규정해도 구현이 없으면 헤더는 조용히 무시되고, 문서만 보고 재시도를 안전하다고 판단하게 된다</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>18.45 운영 실측(같은 요청 4회 → 원가 실적 4행)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-27)** — sys_idempotency + 키 선점 방식 구현, 원가 실적·임시 열람 부여에 적용. 잔여 생성 계열은 위험 순으로. 트리거: 생성 엔드포인트를 만들 때 — 중복 생성이 금액·권한·문서에 영향을 주면 Idempotency-Key 를 적용한다. **키는 작업 전에 선점**한다(작업 후 저장하면 동시 요청 둘 다 실행된다). 규약이 문서에만 있고 구현이 없는지 주기적으로 확인한다.</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J45" s="20" t="inlineStr">
         <is>
-          <t>**부분 해소(2026-07-27)** — sys_idempotency + 키 선점 방식 구현, 원가 실적·임시 열람 부여에 적용. 잔여 생성 계열은 위험 순으로. 트리거: 생성 엔드포인트를 만들 때 — 중복 생성이 금액·권한·문서에 영향을 주면 Idempotency-Key 를 적용한다. **키는 작업 전에 선점**한다(작업 후 저장하면 동시 요청 둘 다 실행된다). 규약이 문서에만 있고 구현이 없는지 주기적으로 확인한다.</t>
+          <t>**부분 해소(2026-07-27)** — sys_idempotency + 키 선점 방식 구현, 원가 실적·임시 열람 부여에 적용. 18.48 로 발주·QCR·Rev-up 추가(누적 5종). 잔여 생성 계열은 중복이 금액·권한·문서에 영향을 주는지로 판단해 이어간다. 트리거: 생성 엔드포인트를 만들 때 — 중복 생성이 금액·권한·문서에 영향을 주면 Idempotency-Key 를 적용한다. **키는 작업 전에 선점**한다(작업 후 저장하면 동시 요청 둘 다 실행된다). 규약이 문서에만 있고 구현이 없는지 주기적으로 확인한다.</t>
         </is>
       </c>
       <c r="K45" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3700,6 +3700,140 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>R-45</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>보안(세션 무효화)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>비밀번호를 바꿔도 이미 열린 세션이 남으면 계정 탈취 대응이 되지 않는다 — 옛 비밀번호 로그인만 막히고 기존 토큰은 수명이 다할 때까지 통한다</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>18.51 운영 실측(재설정 후 옛 토큰 200, 최대 8시간)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — pw_changed_at 기준으로 그 이전 발급 토큰 차단(관리자 재설정 경로). 기존 계정은 NULL 이라 소급 차단하지 않는다. 트리거: 계정 상태·자격을 바꾸는 조작을 만들 때 — **이미 열린 세션에도 반영되는지** 확인한다(비활성화는 되는데 비밀번호는 안 되는 식의 불일치가 실제로 있었다).</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M46" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>R-46</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>배포 안전(클라이언트 계약)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>서버가 세션·토큰 계약을 바꾸면 **아직 대응하지 않은 클라이언트가 깨진다**. 새 값을 응답에 담아도 쓰지 않는 호출자가 있으면 깨지는 변경이고, 인증 실패가 연쇄되면 계정 잠금까지 간다</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>18.54 사고(본인 비밀번호 변경 → 데모 계정 LOCKED · 플릿 130/141)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 본인 변경 경로를 되돌리고 관리자 재설정만 유지. 트리거: 서버 변경이 클라이언트의 기존 호출을 무효화하면 **클라이언트 대응이 선행돼야 한다**. 응답에 새 값을 추가하는 것만으로는 부족하다 — 쓰지 않는 호출자가 남아 있는지 확인한다. 보안 개선이 가용성을 깨지 않게 한다(9.96 해시 승격에서 세운 원칙).</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3834,6 +3834,73 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>R-47</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>테넌트 격리(저장소)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>객체 저장소 키에 테넌트가 없어 **두 테넌트가 같은 프로젝트 번호로 같은 키를 만들 수 있었다**. 프로젝트 번호는 테넌트별 유니크(PS-61313-5 가 양쪽에 존재)이고, 업로드 가드(#53)는 tenant_id 조건으로 조회해 남의 테넌트 객체를 보지 못한다. 충돌 시 앞 테넌트의 행이 남의 바이트를 가리킨다.</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>18.56 정적 확인(키 산식·가드 조건·운영 DB 분포) — 덮어쓰기 실행 실증은 하지 않음</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J48" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — `_storage_key(tid,…)` 로 신규 키를 `t{tid}/` 이름 공간에 두고 Run 산출물도 동일. 기존 행은 저장 경로 유지(마이그레이션 불필요), #53 가드는 신·구 두 경로를 함께 조회. 트리거: 공유 자원(키·파일명·외부 식별자)을 새로 만들 때 테넌트 성분이 있는지 확인. 불변식 검증 `live_storage_ns` 상시 실행(테넌트 간 공유 경로 0건).</t>
+        </is>
+      </c>
+      <c r="K48" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M48" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3901,6 +3901,73 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>R-48</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>테넌트 격리(유지보수 동작)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>테넌트 ADMIN 이 실행하는 유지보수 동작(GC 등)이 공유 자원 전체를 대상으로 삼아 다른 테넌트의 자산에 닿았다. 권한은 테넌트 안에서 정당한데 대상 범위가 테넌트를 넘었다.</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>18.63 실행 실증 — t9999/ 프로브 객체가 테넌트2 ADMIN 의 GC dry-run 에 orphan 으로 잡힘</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 남의 t{N}/ 접두사 객체를 GC 대상에서 제외, foreignSkipped 로 제외 건수 노출. 접두사 없는 옛 객체는 소유 판별 단서가 없어 종전 동작 유지. 트리거: 테넌트 권한으로 실행하는 유지보수·일괄 동작을 추가할 때 **권한 범위와 대상 범위가 같은지** 확인. 검증 live_storage_ns 상시 실행.</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3968,6 +3968,73 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>R-49</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>정보보호(표시 계층)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>서버 통제로 가린 금액이 화면에서 ₩0 으로 표시돼 '가려짐'과 '실제 0원'이 구분되지 않았다. 또 집계 경로(/erp/analytics)가 request 를 받지 않아 열람 모드를 물어볼 수단 자체가 없어 통제 밖에 있었다.</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>18.65~18.66 코드 확인 — sys_info_access 가 비어 있어(기본 full) 현재 데모에서 실제 유출은 없음</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J50" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 공용 포맷터(lib/money.ts)로 가려진 값을 '••••'로 표기하고 가려진 값이 섞인 합계는 내지 않는다. /erp/analytics·/erp/dashboard 에 cost·quote 그룹 적용. 트리거: 금액을 새로 표시하거나 집계 경로를 추가할 때 통제 경유 여부와 표기 방식을 함께 확인. 검증 live_dashboard_masking 상시 실행.</t>
+        </is>
+      </c>
+      <c r="K50" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M50" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4035,6 +4035,73 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>R-50</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>계획 정확도(식별자 층위)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>자재 소요 계획이 재고를 대조하지 못한 코드를 '보유 0'으로 계산해 전 품목을 부족으로 보고했다. 그 계획대로 발주하면 이미 보유한 자재를 중복 구매한다. 원인은 수주 라인(변형 코드)과 마스터·재고(기준 코드)의 식별자 층위 차이.</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>18.73 운영 실측 — 수요 8건 전부 미대조·부족 보고, 창고에는 실재고 존재</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>완화(잔여 위험 있음)</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-27)** — 대조 불가를 UNMATCHED 로 구분해 '보유 0'과 갈랐고 건수를 응답·화면에 노출. **근본 해소는 식별자 체계 결정(#81)에 종속** — 코드 매칭 규칙이 정해져야 소요 대비 재고가 실제로 이어진다. 그 전까지 MRP 는 소요·납기 계획으로만 신뢰하고 재고 대비는 신뢰하지 않는다. 구매요청 화면도 같은 이유로 실수요 전환 보류.</t>
+        </is>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
+          <t>PM/개발</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -4048,12 +4048,12 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>자재 소요 계획이 재고를 대조하지 못한 코드를 '보유 0'으로 계산해 전 품목을 부족으로 보고했다. 그 계획대로 발주하면 이미 보유한 자재를 중복 구매한다. 원인은 수주 라인(변형 코드)과 마스터·재고(기준 코드)의 식별자 층위 차이.</t>
+          <t>자재 소요 계획이 재고를 대조하지 못한 코드를 '보유 0'으로 계산해 부족으로 보고했다(수요 8건 중 5건). 그 계획대로 발주하면 대조하지 못한 품목을 무조건 사게 된다. 원인은 수주 라인(변형 코드)과 마스터·재고(기준 코드)의 식별자 층위 차이.</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>18.73 운영 실측 — 수요 8건 전부 미대조·부족 보고, 창고에는 실재고 존재</t>
+          <t>18.73 운영 실측 — 수요 8건 중 5건 미대조, 나머지 3건은 마스터 존재·실제 재고 0</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4102,6 +4102,73 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>R-51</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>운영(데이터 증가)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>감사 이력·Run 산출물에 보존 정책이 없어 무기한 증가한다. 실측: sys_history 105,655행·34MB(DB 68MB 의 절반, 행당 342B), 산출물 5,508파일·86MB(Run 1회 ≈ 48KB). Run 정리(cleanup)는 메타만 지우고 파일은 남긴다.</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>18.86 운영 실측 — 테이블·객체 크기, 일자별 증가, 동작별 분포</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>완화(잔여 위험 있음)</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-27)** — 증가 요인과 단위 비용을 실측해 결정 항목 #82(산출물 보존)·#83(감사 보존)에 수치로 부착. 정리 동작이 보존되는 파일을 응답에 밝히도록 수정(18.85). **근본 해소는 보존 기간 결정에 종속** — 감사 삭제는 법정/계약 요건이 걸려 개발이 임의로 정할 수 없다. 그 전까지 증가는 계속되며, 백업 용량·복구 시간이 함께 늘어난다.</t>
+        </is>
+      </c>
+      <c r="K52" s="20" t="inlineStr">
+        <is>
+          <t>PM/개발</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M52" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4169,6 +4169,73 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>R-52</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>복구(백업 검증 범위)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>복구 리허설이 DB 덤프만 검증하고 파일(MinIO) 백업은 열어 보지 않은 채 'OK' 를 보고했다. 납품물은 전부 객체 저장소에 있어, 그 상태로는 복구 시 파일 행이 가리키는 바이트가 없는 것을 사전에 알 수 없다.</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>18.88 운영 확인 — 리허설 스크립트에 minio/tar 처리 부재</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>완화</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>**해소(2026-07-27)** — 같은 날짜 MinIO tar 존재·열림·복원 DB 의 file_path 무작위 20건 대조를 리허설에 추가하고 판정을 DB·파일 둘 다로 변경. 통과·실패 경로 모두 실증. 트리거: 백업 대상이 늘면(예: 새 저장소) 리허설 검증 범위도 함께 넓힌다.</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>종결</t>
+        </is>
+      </c>
+      <c r="M53" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_위험관리대장.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4236,6 +4236,73 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>R-53</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>복구(백업 수단·보관 위치)</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>보안관리계획서가 백업 수단으로 명시한 PITR·파일 버전닝이 미구현이라 임의 시점 복구와 덮어써진 객체 회수가 불가하다. 또 백업이 원본과 같은 호스트에만 있어 호스트 소실 시 백업도 함께 잃는다.</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>18.90 실측 — archive_mode=off·wal_level=replica·MinIO versioning None·백업 경로 2곳 모두 동일 호스트</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>심각</t>
+        </is>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t>완화(잔여 위험 있음)</t>
+        </is>
+      </c>
+      <c r="J54" s="20" t="inlineStr">
+        <is>
+          <t>**부분 해소(2026-07-27)** — 문서를 실측과 한계에 맞게 정정해 잘못된 기대를 제거(보안관리계획서·설치배포매뉴얼). RPO 24h·RTO 4h 목표는 일 1회 덤프로 충족함을 실측 확인. **근본 해소는 결정 항목 #85 에 종속** — PITR 도입·버킷 versioning 활성화·원격지 보관은 비용과 운영 방식이 걸린 사용자 결정이다. 그 전까지 덮어써진 객체는 전날 백업 시점으로만 되돌릴 수 있다.</t>
+        </is>
+      </c>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t>PM/개발</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="M54" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
